--- a/pocos/public/payslip-template.xlsx
+++ b/pocos/public/payslip-template.xlsx
@@ -571,12 +571,26 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="34">
+  <borders count="35">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -589,60 +603,67 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <left style="medium"/>
+      <right style="thin"/>
+      <top style="medium"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="medium"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="medium"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="medium"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="medium"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="medium"/>
+      <top style="thin"/>
+      <bottom style="medium"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -658,110 +679,6 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -859,10 +776,36 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -1022,55 +965,55 @@
   </cellStyleXfs>
   <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="distributed"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="distributed"/>
     </xf>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="distributed"/>
     </xf>
     <xf numFmtId="166" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1082,19 +1025,19 @@
     <xf numFmtId="165" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="distributed"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="distributed"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1136,64 +1079,64 @@
     <xf numFmtId="3" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="8" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="167" fontId="12" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="5" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="8" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="5" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="12" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1202,43 +1145,43 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="17" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="17" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="17" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="17" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="17" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="18" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="18" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="18" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="18" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="18" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="18" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="18" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="17" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="17" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="18" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1247,103 +1190,103 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="16" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="16" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="17" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="17" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="18" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="17" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="17" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="18" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="18" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="18" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="18" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="18" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="18" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="18" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="17" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="17" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="18" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="18" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="18" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="18" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="18" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="18" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="17" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="17" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="17" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="18" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="17" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="17" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="18" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="18" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="18" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="18" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="18" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="19" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="170" fontId="19" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="170" fontId="19" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="19" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1373,10 +1316,10 @@
     <xf numFmtId="3" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="8" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="12" fillId="7" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="12" fillId="7" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1388,10 +1331,10 @@
     <xf numFmtId="166" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="8" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1400,10 +1343,10 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="5" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="8" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1758,14 +1701,14 @@
       </c>
     </row>
     <row r="5" ht="23.25" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="8" t="s">
         <v>8</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>5</v>
       </c>
       <c r="D5" s="10"/>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="13" t="s">
         <v>9</v>
       </c>
       <c r="F5" s="12" t="s">
@@ -1773,14 +1716,14 @@
       </c>
     </row>
     <row r="6" ht="23.25" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="8" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>5</v>
       </c>
       <c r="D6" s="10"/>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="13" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="12" t="s">
@@ -1795,7 +1738,7 @@
         <v>5</v>
       </c>
       <c r="D7" s="10"/>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="13" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="12" t="s">
@@ -1810,13 +1753,13 @@
         <v>5</v>
       </c>
       <c r="D8" s="10"/>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="13" t="s">
         <v>15</v>
       </c>
       <c r="F8" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="H8" s="15"/>
+      <c r="H8" s="14"/>
     </row>
     <row r="9" ht="23.25" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" s="8" t="s">
@@ -1826,27 +1769,30 @@
         <v>5</v>
       </c>
       <c r="D9" s="10"/>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="10" ht="23.25" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="10" ht="23.25" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D10" s="1"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="16"/>
     </row>
     <row r="11" ht="23.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="8"/>
       <c r="C11" s="17"/>
       <c r="D11" s="10"/>
-      <c r="E11" s="16"/>
+      <c r="E11" s="13"/>
       <c r="F11" s="18"/>
     </row>
     <row r="12" ht="23.25" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1854,7 +1800,7 @@
       <c r="B12" s="8"/>
       <c r="C12" s="17"/>
       <c r="D12" s="10"/>
-      <c r="E12" s="16"/>
+      <c r="E12" s="13"/>
       <c r="F12" s="18"/>
       <c r="G12" s="19"/>
       <c r="H12" s="19"/>
@@ -1864,7 +1810,7 @@
       <c r="B13" s="8"/>
       <c r="C13" s="10"/>
       <c r="D13" s="10"/>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="13" t="s">
         <v>21</v>
       </c>
       <c r="F13" s="20" t="s">

--- a/pocos/public/payslip-template.xlsx
+++ b/pocos/public/payslip-template.xlsx
@@ -10,6 +10,9 @@
     <sheet sheetId="69" name="D(프리랜서_)" state="visible" r:id="rId4"/>
     <sheet sheetId="81" name="Sheet1" state="visible" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'D(프리랜서_)'!$B1:$F15</definedName>
+  </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
@@ -314,7 +317,7 @@
     <numFmt numFmtId="169" formatCode="_-* #,##0.0_-;-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="170" formatCode="_-* #,##0_-;-* #,##0_-;_-* &quot;-&quot;?_-;_-@_-"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -352,15 +355,6 @@
       <family val="3"/>
       <scheme val="minor"/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
-    </font>
-    <font>
-      <b/>
-      <charset val="129"/>
-      <color theme="1"/>
-      <family val="3"/>
-      <scheme val="minor"/>
-      <sz val="18"/>
       <name val="맑은 고딕"/>
     </font>
     <font>
@@ -921,7 +915,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -984,313 +984,307 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="14" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="14" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="16" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="16" fillId="4" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="16" fillId="4" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="15" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="15" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="16" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="15" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="15" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="15" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="15" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="15" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="15" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="17" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="17" fillId="4" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="17" fillId="4" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="9" fillId="6" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="6" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="4" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1573,7 +1567,10 @@
 
 <file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O16"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:T15"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.625" style="1" customWidth="1"/>
@@ -1594,190 +1591,262 @@
     <col min="45" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
-      <c r="B1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-    </row>
-    <row r="2" ht="29.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="1" t="s">
+    <row r="1" ht="16.5" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1" s="3"/>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+    </row>
+    <row r="2" ht="29.25" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A2" s="3"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-    </row>
-    <row r="3" ht="23.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="4" t="s">
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+    </row>
+    <row r="3" ht="23.25" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" s="3"/>
+      <c r="B3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5" t="s">
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="6"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-    </row>
-    <row r="4" ht="23.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
-      <c r="B4" s="7" t="s">
+      <c r="F3" s="8"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+    </row>
+    <row r="4" ht="23.25" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="3"/>
+      <c r="B4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="10" t="s">
+      <c r="D4" s="11"/>
+      <c r="E4" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-    </row>
-    <row r="5" ht="23.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="7" t="s">
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+    </row>
+    <row r="5" ht="23.25" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" s="3"/>
+      <c r="B5" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="12" t="s">
+      <c r="D5" s="11"/>
+      <c r="E5" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-    </row>
-    <row r="6" ht="23.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="7" t="s">
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+      <c r="S5" s="3"/>
+      <c r="T5" s="3"/>
+    </row>
+    <row r="6" ht="23.25" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A6" s="3"/>
+      <c r="B6" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="9"/>
-      <c r="E6" s="12" t="s">
+      <c r="D6" s="11"/>
+      <c r="E6" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-    </row>
-    <row r="7" ht="23.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
-      <c r="B7" s="7" t="s">
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
+      <c r="S6" s="3"/>
+      <c r="T6" s="3"/>
+    </row>
+    <row r="7" ht="23.25" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A7" s="3"/>
+      <c r="B7" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="12" t="s">
+      <c r="D7" s="11"/>
+      <c r="E7" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-    </row>
-    <row r="8" ht="23.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
-      <c r="B8" s="7" t="s">
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+      <c r="T7" s="3"/>
+    </row>
+    <row r="8" ht="23.25" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A8" s="3"/>
+      <c r="B8" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="12" t="s">
+      <c r="D8" s="11"/>
+      <c r="E8" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="1"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-    </row>
-    <row r="9" ht="23.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
-      <c r="B9" s="7" t="s">
+      <c r="G8" s="3"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+      <c r="S8" s="3"/>
+      <c r="T8" s="3"/>
+    </row>
+    <row r="9" ht="23.25" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9" s="3"/>
+      <c r="B9" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="12" t="s">
+      <c r="D9" s="11"/>
+      <c r="E9" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-    </row>
-    <row r="10" ht="23.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+      <c r="S9" s="3"/>
+      <c r="T9" s="3"/>
+    </row>
+    <row r="10" ht="23.25" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10" s="3"/>
       <c r="B10" s="2" t="s">
         <v>20</v>
       </c>
@@ -1785,107 +1854,138 @@
         <v>5</v>
       </c>
       <c r="D10" s="1"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-    </row>
-    <row r="11" ht="23.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-    </row>
-    <row r="12" ht="23.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-    </row>
-    <row r="13" ht="23.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="9"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3"/>
+      <c r="S10" s="3"/>
+      <c r="T10" s="3"/>
+    </row>
+    <row r="11" ht="23.25" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A11" s="3"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" ht="23.25" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A12" s="3"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3"/>
+      <c r="S12" s="3"/>
+      <c r="T12" s="3"/>
+    </row>
+    <row r="13" ht="23.25" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A13" s="3"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="11"/>
       <c r="D13" s="1"/>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F13" s="19" t="s">
+      <c r="F13" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-    </row>
-    <row r="14" ht="27" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="20"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-    </row>
-    <row r="15" ht="39" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="22" t="s">
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="3"/>
+      <c r="R13" s="3"/>
+      <c r="S13" s="3"/>
+      <c r="T13" s="3"/>
+    </row>
+    <row r="14" ht="27" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A14" s="3"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="3"/>
+      <c r="S14" s="3"/>
+      <c r="T14" s="3"/>
+    </row>
+    <row r="15" ht="39" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A15" s="3"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="F15" s="22"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="23"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-    </row>
-    <row r="16" ht="16.5" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="23"/>
-      <c r="J16" s="23"/>
-      <c r="K16" s="23"/>
-      <c r="L16" s="23"/>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="23"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="25"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="3"/>
+      <c r="S15" s="3"/>
+      <c r="T15" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="5">
